--- a/Универ/4/СА/kr - сделать.XLSX
+++ b/Универ/4/СА/kr - сделать.XLSX
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82C7508-F365-5F4D-B2D2-FCA07C8CE03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="900" windowWidth="21540" windowHeight="15720"/>
+    <workbookView xWindow="48340" yWindow="-12760" windowWidth="35520" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -88,9 +89,6 @@
     <t>&lt;1</t>
   </si>
   <si>
-    <t>Ермоленко Артём Алексеевич 150541 Вариант 6</t>
-  </si>
-  <si>
     <t>К1</t>
   </si>
   <si>
@@ -155,12 +153,15 @@
   </si>
   <si>
     <t>П6 лучше</t>
+  </si>
+  <si>
+    <t>Власов Роман Евгеньевич 250541 Вариант 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -510,26 +511,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M45"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,37 +544,37 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1">
         <v>12</v>
@@ -585,9 +586,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4">
         <f>K12/$K$9</f>
@@ -613,7 +614,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="1">
         <v>9</v>
@@ -625,9 +626,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4">
         <f>$L$9/L4</f>
@@ -653,7 +654,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1">
         <v>15</v>
@@ -665,9 +666,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4">
         <f>M4/$M$9</f>
@@ -693,7 +694,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="1">
         <v>7</v>
@@ -705,7 +706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -716,7 +717,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" s="1">
         <v>10</v>
@@ -728,7 +729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -737,7 +738,7 @@
         <v>0.4</v>
       </c>
       <c r="C9" s="4">
-        <f t="shared" ref="C9:F9" si="0">MIN(C5:C7)</f>
+        <f t="shared" ref="C9" si="0">MIN(C5:C7)</f>
         <v>0.6</v>
       </c>
       <c r="D9" s="4">
@@ -745,11 +746,11 @@
         <v>0.45454545454545453</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="0"/>
+        <f>MIN(E5:E7)</f>
         <v>0.46666666666666667</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="0"/>
+        <f>MIN(F5:F7)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="G9" s="1"/>
@@ -773,7 +774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -786,7 +787,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,25 +801,25 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="M11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -826,7 +827,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K12" s="1">
         <v>9</v>
@@ -838,9 +839,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4">
         <f>K12/$K$15</f>
@@ -860,7 +861,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="1">
         <v>7</v>
@@ -872,9 +873,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4">
         <f>$L$15/L12</f>
@@ -894,7 +895,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K14" s="1">
         <v>10</v>
@@ -906,9 +907,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4">
         <f>M12/$M$15</f>
@@ -941,7 +942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="19" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -954,7 +955,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="10"/>
     </row>
-    <row r="17" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -967,9 +968,9 @@
       <c r="J17" s="1"/>
       <c r="K17" s="10"/>
     </row>
-    <row r="18" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6">
         <f>SUM(B13:D13)/3</f>
@@ -977,7 +978,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="6">
         <f>(ABS(B13-B18)+ABS(C13-B18)+ABS(D13-B18))/(3*B18)</f>
@@ -985,7 +986,7 @@
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H18" s="6">
         <f>E18/$E$21</f>
@@ -995,9 +996,9 @@
       <c r="J18" s="1"/>
       <c r="K18" s="10"/>
     </row>
-    <row r="19" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6">
         <f>SUM(B14:D14)/3</f>
@@ -1005,7 +1006,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" s="6">
         <f>(ABS(B14-B19)+ABS(C14-B19)+ABS(D14-B19))/(3*B19)</f>
@@ -1013,7 +1014,7 @@
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="6">
         <f>E19/$E$21</f>
@@ -1023,9 +1024,9 @@
       <c r="J19" s="1"/>
       <c r="K19" s="10"/>
     </row>
-    <row r="20" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="6">
         <f>SUM(B15:D15)/3</f>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="6">
         <f>(ABS(B15-B20)+ABS(C15-B20)+ABS(D15-B20))/(3*B20)</f>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H20" s="6">
         <f>E20/$E$21</f>
@@ -1051,12 +1052,12 @@
       <c r="J20" s="1"/>
       <c r="K20" s="10"/>
     </row>
-    <row r="21" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" s="6">
         <f>SUM(E18:E20)</f>
@@ -1069,7 +1070,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="10"/>
     </row>
-    <row r="22" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1082,7 +1083,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="10"/>
     </row>
-    <row r="23" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1097,16 +1098,16 @@
       <c r="J23" s="1"/>
       <c r="K23" s="10"/>
     </row>
-    <row r="24" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1114,9 +1115,9 @@
       <c r="J24" s="1"/>
       <c r="K24" s="10"/>
     </row>
-    <row r="25" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="7">
         <f>$H$18/B13</f>
@@ -1141,9 +1142,9 @@
       <c r="J25" s="1"/>
       <c r="K25" s="10"/>
     </row>
-    <row r="26" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="7">
         <f>$H$19/B14</f>
@@ -1168,9 +1169,9 @@
       <c r="J26" s="1"/>
       <c r="K26" s="10"/>
     </row>
-    <row r="27" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="7">
         <f>$H$20/B15</f>
@@ -1195,7 +1196,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="10"/>
     </row>
-    <row r="28" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1208,7 +1209,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="10"/>
     </row>
-    <row r="29" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1221,13 +1222,13 @@
       <c r="J29" s="1"/>
       <c r="K29" s="10"/>
     </row>
-    <row r="30" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1238,9 +1239,9 @@
       <c r="J30" s="1"/>
       <c r="K30" s="10"/>
     </row>
-    <row r="31" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="8">
         <v>9</v>
@@ -1266,9 +1267,9 @@
       <c r="J31" s="1"/>
       <c r="K31" s="10"/>
     </row>
-    <row r="32" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="8">
         <v>120</v>
@@ -1294,7 +1295,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="10"/>
     </row>
-    <row r="33" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1307,7 +1308,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="10"/>
     </row>
-    <row r="34" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>10</v>
       </c>
@@ -1327,7 +1328,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="10"/>
     </row>
-    <row r="35" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>11</v>
       </c>
@@ -1347,7 +1348,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="10"/>
     </row>
-    <row r="36" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1357,7 +1358,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="10"/>
     </row>
-    <row r="37" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>14</v>
       </c>
@@ -1375,7 +1376,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="10"/>
     </row>
-    <row r="38" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>15</v>
       </c>
@@ -1393,7 +1394,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="10"/>
     </row>
-    <row r="39" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>16</v>
       </c>
@@ -1405,7 +1406,7 @@
         <v>18</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1415,7 +1416,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="10"/>
     </row>
-    <row r="40" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1423,7 +1424,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="10"/>
     </row>
-    <row r="41" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -1431,7 +1432,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="10"/>
     </row>
-    <row r="42" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -1439,7 +1440,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="10"/>
     </row>
-    <row r="43" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="19" x14ac:dyDescent="0.25">
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -1447,13 +1448,13 @@
       <c r="J43" s="1"/>
       <c r="K43" s="10"/>
     </row>
-    <row r="44" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
